--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20261012.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20261012.xlsx
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>1,196,000</t>
+          <t>18,481,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>18,481,000</t>
+          <t>1,973,678</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>1,973,678</t>
+          <t>1,196,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>17,752,000</t>
+          <t>16,273,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>16,273,000</t>
+          <t>17,752,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>遠百</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>7,925,000</t>
+          <t>36,534,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>遠百</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>36,534,000</t>
+          <t>7,925,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
